--- a/XML/2026/CIV1009089B0-EMITIDOS-GENERAL-SIN-NOMINAS-PAGOS-DEL-01-01-2026-AL-01-10-2026.xlsx
+++ b/XML/2026/CIV1009089B0-EMITIDOS-GENERAL-SIN-NOMINAS-PAGOS-DEL-01-01-2026-AL-01-10-2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3837" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4403" uniqueCount="763">
   <si>
     <t>Periodo</t>
   </si>
@@ -1774,12 +1774,6 @@
     <t>2026-08-13 14:05:34</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>N/A - Motivo de cancelación desconocido</t>
-  </si>
-  <si>
     <t>5348F335-213A-43B2-9C97-72B7733712BB</t>
   </si>
   <si>
@@ -2018,6 +2012,294 @@
   </si>
   <si>
     <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA TRAMO MEXICO-QUERETARO, LA CANTIDAD DE $1,004,937.90 (UN MILLON CUATRO MIL NOVECIENTOS TREINTA Y SIETE PESOS 90/100 M.N.)  POR CONCEPTO DE PAGO DE LA ESTIMACIÓN No. 2 (DOS), CON UN PERIODO DE EJECUCION DEL 01 AL 15 DE AGOSTO DE 2026, DE LOS TRABAJOS DE SUMINISTRO Y APLICACIÓN DE PINTURA DE TRÁNSITO DE ALTO DESEMPEÑO Y PINTURA TERMOPLÁSTICA EN LA UNIDAD REGIONAL ESTADO DE MÉXICO. CON NÚMERO DE CONTRATO 4500037720  DE FECHA 06 DE JULIO DE 2026.Importe de estimación estimación 2 (DOS): $864,029.65 Importe de la devolución de la retención del periodo anteriro: $2,296.13 subtotal 1: $866,325.78 </t>
+  </si>
+  <si>
+    <t>A51F6C73-1BA8-48F4-A310-DB13B15E326C</t>
+  </si>
+  <si>
+    <t>2026-09-09 09:50:28</t>
+  </si>
+  <si>
+    <t>2026-09-09 09:50:33</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20398</t>
+  </si>
+  <si>
+    <t>D46353EF-2561-441C-BC2D-787458C18FB1</t>
+  </si>
+  <si>
+    <t>2026-09-09 09:58:53</t>
+  </si>
+  <si>
+    <t>2026-09-09 09:58:58</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA:20455</t>
+  </si>
+  <si>
+    <t>70AF0FBD-D2D3-481A-80D4-B06A2D6EF68A</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:05:16</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:05:20</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20461</t>
+  </si>
+  <si>
+    <t>4CB9D40C-FDD6-4044-8B45-42D41EF14E6E</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:09:08</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:09:12</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20465</t>
+  </si>
+  <si>
+    <t>62AE83E2-4C68-4762-87A5-0ED19747053F</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:13:33</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:13:36</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20470</t>
+  </si>
+  <si>
+    <t>8D41C870-D53C-4DB0-AF7A-935BA5D55661</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:20:40</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:20:42</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20473</t>
+  </si>
+  <si>
+    <t>974FD959-0B82-4184-946D-015461BA1B7B</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:26:52</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:26:55</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20508</t>
+  </si>
+  <si>
+    <t>064ADF9D-AC10-43D9-8C6D-4174004BC991</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:30:54</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:30:57</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20532</t>
+  </si>
+  <si>
+    <t>9725B4BB-B269-43AE-BEBD-3E267C4AD018</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:36:03</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:36:06</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20544</t>
+  </si>
+  <si>
+    <t>1910711D-DF1A-4C15-858A-4599FFED5D0E</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:40:19</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:40:23</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20548</t>
+  </si>
+  <si>
+    <t>3710771F-195E-449C-BB44-2AF6B1B8E5E5</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:46:38</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:46:40</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20562</t>
+  </si>
+  <si>
+    <t>7BDDC671-3E97-4267-86AA-D7EB875994FB</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:51:35</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:51:38</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20619</t>
+  </si>
+  <si>
+    <t>77A3FA2F-5D07-461C-B041-1FFC3C3AF981</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:56:19</t>
+  </si>
+  <si>
+    <t>2026-09-09 10:56:22</t>
+  </si>
+  <si>
+    <t>. 7% DE USO DE ALMACÉN Y DE FLETES DE LA  ORDEN DE COMPRA: 20639</t>
+  </si>
+  <si>
+    <t>C27F2A7E-9818-462B-836F-970786FDD2DB</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>2026-09-09 17:47:54</t>
+  </si>
+  <si>
+    <t>2026-09-09 17:47:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA TRAMO MEXICO-QUERETARO, LA CANTIDAD DE $526,635.67 (QUINIENTOS VEINTISEIS MIL SEISCIENTOS TREINTA Y CINCO PESOS 67/100 M.N.)  POR CONCEPTO DE PAGO DE LA ESTIMACIÓN No. 3 (TRES), CON UN PERIODO DE EJECUCION DEL 16 AL 31 DE AGOSTO DE 2026, DE LOS TRABAJOS DE SUMINISTRO Y APLICACIÓN DE PINTURA DE TRÁNSITO DE ALTO DESEMPEÑO Y PINTURA TERMOPLÁSTICA EN LA UNIDAD REGIONAL ESTADO DE MÉXICO. CON NÚMERO DE CONTRATO 4500037720  DE FECHA 06 DE JULIO DE 2026.Importe de estimación 3 (TRES): $458,159.90 Importe de retención de este periodo : -$4,163.63  subtotal 1: $453,996.27 </t>
+  </si>
+  <si>
+    <t>7EAA0452-D5BF-4822-80C9-CACCE4BC282D</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>2026-09-10 12:17:58</t>
+  </si>
+  <si>
+    <t>2026-09-10 12:18:02</t>
+  </si>
+  <si>
+    <t>RECIBI SUMINISTRO DE DEFENSA METALICA DE 3 CRESTAS Y ACCESORIOS CON TORNILLERIA PARA STOCK DE APP LA GLORIA.</t>
+  </si>
+  <si>
+    <t>E7FFE9F6-ADB5-44BB-B02D-5B4F82095E82</t>
+  </si>
+  <si>
+    <t>04 - Sustitución de CFDI previos.</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>2026-09-18 13:20:37</t>
+  </si>
+  <si>
+    <t>2026-09-18 13:20:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA TRAMO MEXICO-QUERETARO, LA CANTIDAD DE $526,641.57 (QUINIENTOS VEINTISEIS MIL SEISCIENTOS CUARENTA Y UN PESOS 57/100 M.N.)  POR CONCEPTO DE PAGO DE LA ESTIMACIÓN No. 3 (TRES), CON UN PERIODO DE EJECUCION DEL 16 AL 31 DE AGOSTO DE 2026, DE LOS TRABAJOS DE SUMINISTRO Y APLICACIÓN DE PINTURA DE TRÁNSITO DE ALTO DESEMPEÑO Y PINTURA TERMOPLÁSTICA EN LA UNIDAD REGIONAL ESTADO DE MÉXICO. CON NÚMERO DE CONTRATO 4500037720  DE FECHA 06 DE JULIO DE 2026.Importe de estimación estimación 3 (TRES): $458,164.98 Importe de retención de esta estimación estimación 3: -$4,163.63 subtotal 1: $454,001.35 </t>
+  </si>
+  <si>
+    <t>2026-09-18 15:28:20</t>
+  </si>
+  <si>
+    <t>F4C9CEF8-0334-4F3E-A580-4593175F5155</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>2026-09-18 15:30:08</t>
+  </si>
+  <si>
+    <t>2026-09-18 15:30:11</t>
+  </si>
+  <si>
+    <t>2026-09-18 15:30:35</t>
+  </si>
+  <si>
+    <t>04F8CA0B-E232-44A2-80F9-94A531BF14D9</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>2026-09-18 15:31:46</t>
+  </si>
+  <si>
+    <t>2026-09-18 15:31:48</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:11:39</t>
+  </si>
+  <si>
+    <t>SOLICITUD RECHAZADA</t>
+  </si>
+  <si>
+    <t>77EC2FED-82A0-4444-98F9-500FBB68CC50</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>2026-09-21 17:14:19</t>
+  </si>
+  <si>
+    <t>2026-09-21 17:14:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA TRAMO MEXICO-QUERETARO, LA CANTIDAD DE $526,641.57 (QUINIENTOS VEINTISEIS MIL SEISCIENTOS CUARENTA Y UN PESOS 57/100 M.N.)  POR CONCEPTO DE PAGO DE LA ESTIMACIÓN No. 3 (TRES), CON UN PERIODO DE EJECUCION DEL 16 AL 31 DE AGOSTO DE 2026, DE LOS TRABAJOS DE SUMINISTRO Y APLICACIÓN DE PINTURA DE TRÁNSITO DE ALTO DESEMPEÑO Y PINTURA TERMOPLÁSTICA EN LA UNIDAD REGIONAL ESTADO DE MÉXICO. CON NÚMERO DE CONTRATO 4500037720  DE FECHA 06 DE JULIO DE 2026.Importe de estimación estimación 3 (TRES): $458,164.98 Importe de retención de esta estimación estimación 3 (TRES): -$4,163.63 subtotal 1: $454,001.35 </t>
+  </si>
+  <si>
+    <t>C4B01239-340D-4D70-8C6B-8742A3DB700B</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2026-10-01 11:34:03</t>
+  </si>
+  <si>
+    <t>2026-10-01 11:34:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA LA CANTIDAD DE $9,277,722.07 (NUEVE MILLONES DOSCIENTOSSETENTA Y SIETE MIL SETECIENTOS VEINTIDÓS PESOS 07/100 M.N.) POR CONCEPTO DE PAGO DE LA ESTIMACIÓN 06 (SEIS) CORRESPONDIENTE AL PERIODO DE 01 AL 15 DE SEPTIEMBRE DE 2026 REFERENTE A LOS SERVICIOS DE "SEGURIDAD CARRETERA EN LA UNIDAD REGIONAL HERMOSILLO, INCLUYE: COLOCACIÓN DE DISPOSITIVOS DE SEGURIDAD VIAL Y SEÑALAMIENTO HORIZONTAL, TRAMO: HERMOSILLO - GUAYMAS"AMPARADO BAJO EL CONTRATO 4500037673 DE FECHA 29 DE JUNIO DE 2026IMPORTE DE LA ESTIMACIÓN No.6 (SEIS) $7,968,870.00 RETENCIÓN EN ESTIMACIÓN 6 (SEIS) $29,166.27 SUBTOTAL $7,998,036.27 </t>
+  </si>
+  <si>
+    <t>2026-10-01 14:16:16</t>
+  </si>
+  <si>
+    <t>21978BF7-5153-40FB-86D1-D889DE1D1140</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2026-10-01 14:18:15</t>
+  </si>
+  <si>
+    <t>2026-10-01 14:18:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIBI DEL FONDO NACIONAL DE INFRAESTRUCTURA LA CANTIDAD DE $9,277,722.07 (NUEVE MILLONES DOSCIENTOSSETENTA Y SIETE MIL SETECIENTOS VEINTIDÓS PESOS 07/100 M.N.) POR CONCEPTO DE PAGO DE LA ESTIMACIÓN 06 (SEIS) CORRESPONDIENTE AL PERIODO DE 01 AL 15 DE SEPTIEMBRE DE 2026 REFERENTE A LOS SERVICIOS DE "SEGURIDAD CARRETERA EN LA UNIDAD REGIONAL HERMOSILLO, INCLUYE: COLOCACIÓN DE DISPOSITIVOS DE SEGURIDAD VIAL Y SEÑALAMIENTO HORIZONTAL, TRAMO: HERMOSILLO - GUAYMAS"AMPARADO BAJO EL CONTRATO 4500037673 DE FECHA 29 DE JUNIO DE 2026IMPORTE DE LA ESTIMACIÓN No.6 (SEIS) $7,968,870.00 RETENCIÓN EN ESTIMACIÓN 6 (SEIS) $-DEVOLUCION DE LA RETENCION $29,166.27SUBTOTAL $7,998,036.27 </t>
   </si>
 </sst>
 </file>
@@ -2394,7 +2676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ135"/>
+  <dimension ref="A1:AQ156"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -16082,19 +16364,13 @@
         <v>61</v>
       </c>
       <c r="Z118" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA118" t="s">
         <v>62</v>
       </c>
-      <c r="AB118" t="s">
-        <v>587</v>
-      </c>
       <c r="AC118" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD118" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE118" t="s">
         <v>63</v>
@@ -16144,7 +16420,7 @@
         <v>43</v>
       </c>
       <c r="C119" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D119" t="s">
         <v>45</v>
@@ -16153,16 +16429,16 @@
         <v>46</v>
       </c>
       <c r="H119" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="I119" t="s">
         <v>48</v>
       </c>
       <c r="J119" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="K119" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="L119" t="s">
         <v>51</v>
@@ -16204,19 +16480,13 @@
         <v>61</v>
       </c>
       <c r="Z119" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA119" t="s">
         <v>62</v>
       </c>
-      <c r="AB119" t="s">
-        <v>587</v>
-      </c>
       <c r="AC119" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD119" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE119" t="s">
         <v>63</v>
@@ -16266,7 +16536,7 @@
         <v>43</v>
       </c>
       <c r="C120" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D120" t="s">
         <v>45</v>
@@ -16275,16 +16545,16 @@
         <v>46</v>
       </c>
       <c r="H120" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I120" t="s">
         <v>48</v>
       </c>
       <c r="J120" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="K120" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L120" t="s">
         <v>51</v>
@@ -16311,10 +16581,10 @@
         <v>73</v>
       </c>
       <c r="T120" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="U120" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="V120" t="s">
         <v>60</v>
@@ -16326,19 +16596,13 @@
         <v>61</v>
       </c>
       <c r="Z120" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA120" t="s">
         <v>62</v>
       </c>
-      <c r="AB120" t="s">
-        <v>587</v>
-      </c>
       <c r="AC120" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD120" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE120" t="s">
         <v>63</v>
@@ -16388,7 +16652,7 @@
         <v>43</v>
       </c>
       <c r="C121" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D121" t="s">
         <v>45</v>
@@ -16397,16 +16661,16 @@
         <v>46</v>
       </c>
       <c r="H121" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I121" t="s">
         <v>48</v>
       </c>
       <c r="J121" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K121" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L121" t="s">
         <v>51</v>
@@ -16448,19 +16712,13 @@
         <v>61</v>
       </c>
       <c r="Z121" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA121" t="s">
         <v>62</v>
       </c>
-      <c r="AB121" t="s">
-        <v>587</v>
-      </c>
       <c r="AC121" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD121" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE121" t="s">
         <v>63</v>
@@ -16510,7 +16768,7 @@
         <v>43</v>
       </c>
       <c r="C122" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D122" t="s">
         <v>45</v>
@@ -16519,16 +16777,16 @@
         <v>46</v>
       </c>
       <c r="H122" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I122" t="s">
         <v>48</v>
       </c>
       <c r="J122" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K122" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L122" t="s">
         <v>51</v>
@@ -16555,10 +16813,10 @@
         <v>73</v>
       </c>
       <c r="T122" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="U122" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="V122" t="s">
         <v>60</v>
@@ -16570,19 +16828,13 @@
         <v>61</v>
       </c>
       <c r="Z122" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA122" t="s">
         <v>62</v>
       </c>
-      <c r="AB122" t="s">
-        <v>587</v>
-      </c>
       <c r="AC122" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD122" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE122" t="s">
         <v>63</v>
@@ -16632,7 +16884,7 @@
         <v>43</v>
       </c>
       <c r="C123" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D123" t="s">
         <v>45</v>
@@ -16641,16 +16893,16 @@
         <v>46</v>
       </c>
       <c r="H123" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="I123" t="s">
         <v>48</v>
       </c>
       <c r="J123" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K123" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L123" t="s">
         <v>51</v>
@@ -16692,19 +16944,13 @@
         <v>61</v>
       </c>
       <c r="Z123" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA123" t="s">
         <v>62</v>
       </c>
-      <c r="AB123" t="s">
-        <v>587</v>
-      </c>
       <c r="AC123" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD123" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE123" t="s">
         <v>63</v>
@@ -16754,7 +17000,7 @@
         <v>43</v>
       </c>
       <c r="C124" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D124" t="s">
         <v>45</v>
@@ -16763,16 +17009,16 @@
         <v>46</v>
       </c>
       <c r="H124" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I124" t="s">
         <v>48</v>
       </c>
       <c r="J124" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="K124" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="L124" t="s">
         <v>51</v>
@@ -16814,19 +17060,13 @@
         <v>61</v>
       </c>
       <c r="Z124" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA124" t="s">
         <v>62</v>
       </c>
-      <c r="AB124" t="s">
-        <v>587</v>
-      </c>
       <c r="AC124" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD124" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE124" t="s">
         <v>63</v>
@@ -16876,7 +17116,7 @@
         <v>43</v>
       </c>
       <c r="C125" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D125" t="s">
         <v>45</v>
@@ -16885,16 +17125,16 @@
         <v>46</v>
       </c>
       <c r="H125" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="I125" t="s">
         <v>48</v>
       </c>
       <c r="J125" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="K125" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L125" t="s">
         <v>51</v>
@@ -16936,19 +17176,13 @@
         <v>61</v>
       </c>
       <c r="Z125" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA125" t="s">
         <v>62</v>
       </c>
-      <c r="AB125" t="s">
-        <v>587</v>
-      </c>
       <c r="AC125" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD125" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE125" t="s">
         <v>63</v>
@@ -16998,7 +17232,7 @@
         <v>43</v>
       </c>
       <c r="C126" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D126" t="s">
         <v>45</v>
@@ -17007,16 +17241,16 @@
         <v>46</v>
       </c>
       <c r="H126" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I126" t="s">
         <v>48</v>
       </c>
       <c r="J126" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="K126" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="L126" t="s">
         <v>51</v>
@@ -17058,19 +17292,13 @@
         <v>61</v>
       </c>
       <c r="Z126" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA126" t="s">
         <v>62</v>
       </c>
-      <c r="AB126" t="s">
-        <v>587</v>
-      </c>
       <c r="AC126" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD126" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE126" t="s">
         <v>63</v>
@@ -17120,7 +17348,7 @@
         <v>43</v>
       </c>
       <c r="C127" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D127" t="s">
         <v>45</v>
@@ -17129,16 +17357,16 @@
         <v>46</v>
       </c>
       <c r="H127" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I127" t="s">
         <v>48</v>
       </c>
       <c r="J127" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="K127" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="L127" t="s">
         <v>51</v>
@@ -17180,19 +17408,13 @@
         <v>61</v>
       </c>
       <c r="Z127" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA127" t="s">
         <v>62</v>
       </c>
-      <c r="AB127" t="s">
-        <v>587</v>
-      </c>
       <c r="AC127" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD127" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE127" t="s">
         <v>63</v>
@@ -17242,7 +17464,7 @@
         <v>43</v>
       </c>
       <c r="C128" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D128" t="s">
         <v>45</v>
@@ -17251,16 +17473,16 @@
         <v>46</v>
       </c>
       <c r="H128" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I128" t="s">
         <v>48</v>
       </c>
       <c r="J128" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="K128" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="L128" t="s">
         <v>51</v>
@@ -17302,19 +17524,13 @@
         <v>61</v>
       </c>
       <c r="Z128" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA128" t="s">
         <v>62</v>
       </c>
-      <c r="AB128" t="s">
-        <v>587</v>
-      </c>
       <c r="AC128" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD128" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE128" t="s">
         <v>63</v>
@@ -17364,7 +17580,7 @@
         <v>43</v>
       </c>
       <c r="C129" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D129" t="s">
         <v>45</v>
@@ -17373,16 +17589,16 @@
         <v>46</v>
       </c>
       <c r="H129" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="I129" t="s">
         <v>48</v>
       </c>
       <c r="J129" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K129" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="L129" t="s">
         <v>51</v>
@@ -17424,19 +17640,13 @@
         <v>61</v>
       </c>
       <c r="Z129" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA129" t="s">
         <v>62</v>
       </c>
-      <c r="AB129" t="s">
-        <v>587</v>
-      </c>
       <c r="AC129" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD129" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE129" t="s">
         <v>63</v>
@@ -17486,7 +17696,7 @@
         <v>43</v>
       </c>
       <c r="C130" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D130" t="s">
         <v>45</v>
@@ -17495,16 +17705,16 @@
         <v>46</v>
       </c>
       <c r="H130" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="I130" t="s">
         <v>48</v>
       </c>
       <c r="J130" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K130" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="L130" t="s">
         <v>51</v>
@@ -17546,19 +17756,13 @@
         <v>61</v>
       </c>
       <c r="Z130" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA130" t="s">
         <v>62</v>
       </c>
-      <c r="AB130" t="s">
-        <v>587</v>
-      </c>
       <c r="AC130" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD130" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE130" t="s">
         <v>63</v>
@@ -17608,7 +17812,7 @@
         <v>43</v>
       </c>
       <c r="C131" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D131" t="s">
         <v>45</v>
@@ -17617,16 +17821,16 @@
         <v>46</v>
       </c>
       <c r="H131" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I131" t="s">
         <v>48</v>
       </c>
       <c r="J131" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="K131" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="L131" t="s">
         <v>51</v>
@@ -17668,19 +17872,13 @@
         <v>61</v>
       </c>
       <c r="Z131" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA131" t="s">
         <v>62</v>
       </c>
-      <c r="AB131" t="s">
-        <v>587</v>
-      </c>
       <c r="AC131" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD131" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE131" t="s">
         <v>63</v>
@@ -17730,7 +17928,7 @@
         <v>43</v>
       </c>
       <c r="C132" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D132" t="s">
         <v>45</v>
@@ -17739,16 +17937,16 @@
         <v>46</v>
       </c>
       <c r="H132" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I132" t="s">
         <v>48</v>
       </c>
       <c r="J132" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="K132" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="L132" t="s">
         <v>51</v>
@@ -17790,19 +17988,13 @@
         <v>61</v>
       </c>
       <c r="Z132" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA132" t="s">
         <v>62</v>
       </c>
-      <c r="AB132" t="s">
-        <v>587</v>
-      </c>
       <c r="AC132" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD132" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE132" t="s">
         <v>63</v>
@@ -17852,7 +18044,7 @@
         <v>43</v>
       </c>
       <c r="C133" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D133" t="s">
         <v>45</v>
@@ -17861,16 +18053,16 @@
         <v>46</v>
       </c>
       <c r="H133" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I133" t="s">
         <v>48</v>
       </c>
       <c r="J133" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="K133" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L133" t="s">
         <v>51</v>
@@ -17900,7 +18092,7 @@
         <v>575</v>
       </c>
       <c r="U133" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="V133" t="s">
         <v>60</v>
@@ -17968,7 +18160,7 @@
         <v>43</v>
       </c>
       <c r="C134" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D134" t="s">
         <v>45</v>
@@ -17977,16 +18169,16 @@
         <v>46</v>
       </c>
       <c r="H134" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I134" t="s">
         <v>48</v>
       </c>
       <c r="J134" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="K134" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L134" t="s">
         <v>51</v>
@@ -18001,13 +18193,13 @@
         <v>54</v>
       </c>
       <c r="P134" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>657</v>
+      </c>
+      <c r="R134" t="s">
         <v>658</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>659</v>
-      </c>
-      <c r="R134" t="s">
-        <v>660</v>
       </c>
       <c r="S134" t="s">
         <v>46</v>
@@ -18016,10 +18208,10 @@
         <v>575</v>
       </c>
       <c r="U134" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="V134" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="W134" t="s">
         <v>45</v>
@@ -18049,7 +18241,7 @@
         <v>94</v>
       </c>
       <c r="AI134" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AJ134">
         <v>2687.12</v>
@@ -18084,7 +18276,7 @@
         <v>43</v>
       </c>
       <c r="C135" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D135" t="s">
         <v>45</v>
@@ -18093,16 +18285,16 @@
         <v>46</v>
       </c>
       <c r="H135" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="I135" t="s">
         <v>48</v>
       </c>
       <c r="J135" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K135" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="L135" t="s">
         <v>51</v>
@@ -18132,7 +18324,7 @@
         <v>575</v>
       </c>
       <c r="U135" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="V135" t="s">
         <v>60</v>
@@ -18144,19 +18336,13 @@
         <v>61</v>
       </c>
       <c r="Z135" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AA135" t="s">
         <v>62</v>
       </c>
-      <c r="AB135" t="s">
-        <v>587</v>
-      </c>
       <c r="AC135" t="s">
-        <v>588</v>
-      </c>
-      <c r="AD135" t="s">
-        <v>587</v>
+        <v>45</v>
       </c>
       <c r="AE135" t="s">
         <v>63</v>
@@ -18196,6 +18382,2472 @@
       </c>
       <c r="AQ135">
         <v>998889.69</v>
+      </c>
+    </row>
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>9</v>
+      </c>
+      <c r="B136" t="s">
+        <v>43</v>
+      </c>
+      <c r="C136" t="s">
+        <v>667</v>
+      </c>
+      <c r="D136" t="s">
+        <v>591</v>
+      </c>
+      <c r="E136" t="s">
+        <v>196</v>
+      </c>
+      <c r="F136" t="s">
+        <v>46</v>
+      </c>
+      <c r="I136" t="s">
+        <v>87</v>
+      </c>
+      <c r="J136" t="s">
+        <v>668</v>
+      </c>
+      <c r="K136" t="s">
+        <v>669</v>
+      </c>
+      <c r="L136" t="s">
+        <v>51</v>
+      </c>
+      <c r="M136" t="s">
+        <v>52</v>
+      </c>
+      <c r="N136" t="s">
+        <v>53</v>
+      </c>
+      <c r="O136" t="s">
+        <v>54</v>
+      </c>
+      <c r="P136" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>72</v>
+      </c>
+      <c r="R136" t="s">
+        <v>52</v>
+      </c>
+      <c r="S136" t="s">
+        <v>73</v>
+      </c>
+      <c r="T136" t="s">
+        <v>90</v>
+      </c>
+      <c r="U136" t="s">
+        <v>670</v>
+      </c>
+      <c r="V136" t="s">
+        <v>92</v>
+      </c>
+      <c r="W136" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA136" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC136" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE136" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF136">
+        <v>1</v>
+      </c>
+      <c r="AG136" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH136" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI136" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ136">
+        <v>-222.88</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>-35.66</v>
+      </c>
+      <c r="AM136">
+        <v>0</v>
+      </c>
+      <c r="AN136">
+        <v>0</v>
+      </c>
+      <c r="AO136">
+        <v>0</v>
+      </c>
+      <c r="AP136">
+        <v>0</v>
+      </c>
+      <c r="AQ136">
+        <v>-258.54</v>
+      </c>
+    </row>
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>9</v>
+      </c>
+      <c r="B137" t="s">
+        <v>43</v>
+      </c>
+      <c r="C137" t="s">
+        <v>671</v>
+      </c>
+      <c r="D137" t="s">
+        <v>597</v>
+      </c>
+      <c r="E137" t="s">
+        <v>196</v>
+      </c>
+      <c r="F137" t="s">
+        <v>46</v>
+      </c>
+      <c r="I137" t="s">
+        <v>87</v>
+      </c>
+      <c r="J137" t="s">
+        <v>672</v>
+      </c>
+      <c r="K137" t="s">
+        <v>673</v>
+      </c>
+      <c r="L137" t="s">
+        <v>51</v>
+      </c>
+      <c r="M137" t="s">
+        <v>52</v>
+      </c>
+      <c r="N137" t="s">
+        <v>53</v>
+      </c>
+      <c r="O137" t="s">
+        <v>54</v>
+      </c>
+      <c r="P137" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>72</v>
+      </c>
+      <c r="R137" t="s">
+        <v>52</v>
+      </c>
+      <c r="S137" t="s">
+        <v>73</v>
+      </c>
+      <c r="T137" t="s">
+        <v>90</v>
+      </c>
+      <c r="U137" t="s">
+        <v>674</v>
+      </c>
+      <c r="V137" t="s">
+        <v>92</v>
+      </c>
+      <c r="W137" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA137" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC137" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE137" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF137">
+        <v>1</v>
+      </c>
+      <c r="AG137" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH137" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI137" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ137">
+        <v>-2821.47</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>-451.44</v>
+      </c>
+      <c r="AM137">
+        <v>0</v>
+      </c>
+      <c r="AN137">
+        <v>0</v>
+      </c>
+      <c r="AO137">
+        <v>0</v>
+      </c>
+      <c r="AP137">
+        <v>0</v>
+      </c>
+      <c r="AQ137">
+        <v>-3272.91</v>
+      </c>
+    </row>
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
+        <v>43</v>
+      </c>
+      <c r="C138" t="s">
+        <v>675</v>
+      </c>
+      <c r="D138" t="s">
+        <v>601</v>
+      </c>
+      <c r="E138" t="s">
+        <v>196</v>
+      </c>
+      <c r="F138" t="s">
+        <v>46</v>
+      </c>
+      <c r="I138" t="s">
+        <v>87</v>
+      </c>
+      <c r="J138" t="s">
+        <v>676</v>
+      </c>
+      <c r="K138" t="s">
+        <v>677</v>
+      </c>
+      <c r="L138" t="s">
+        <v>51</v>
+      </c>
+      <c r="M138" t="s">
+        <v>52</v>
+      </c>
+      <c r="N138" t="s">
+        <v>53</v>
+      </c>
+      <c r="O138" t="s">
+        <v>54</v>
+      </c>
+      <c r="P138" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>72</v>
+      </c>
+      <c r="R138" t="s">
+        <v>52</v>
+      </c>
+      <c r="S138" t="s">
+        <v>73</v>
+      </c>
+      <c r="T138" t="s">
+        <v>90</v>
+      </c>
+      <c r="U138" t="s">
+        <v>678</v>
+      </c>
+      <c r="V138" t="s">
+        <v>92</v>
+      </c>
+      <c r="W138" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA138" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC138" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE138" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF138">
+        <v>1</v>
+      </c>
+      <c r="AG138" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH138" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI138" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ138">
+        <v>-2069.09</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>-331.05</v>
+      </c>
+      <c r="AM138">
+        <v>0</v>
+      </c>
+      <c r="AN138">
+        <v>0</v>
+      </c>
+      <c r="AO138">
+        <v>0</v>
+      </c>
+      <c r="AP138">
+        <v>0</v>
+      </c>
+      <c r="AQ138">
+        <v>-2400.14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>9</v>
+      </c>
+      <c r="B139" t="s">
+        <v>43</v>
+      </c>
+      <c r="C139" t="s">
+        <v>679</v>
+      </c>
+      <c r="D139" t="s">
+        <v>607</v>
+      </c>
+      <c r="E139" t="s">
+        <v>196</v>
+      </c>
+      <c r="F139" t="s">
+        <v>46</v>
+      </c>
+      <c r="I139" t="s">
+        <v>87</v>
+      </c>
+      <c r="J139" t="s">
+        <v>680</v>
+      </c>
+      <c r="K139" t="s">
+        <v>681</v>
+      </c>
+      <c r="L139" t="s">
+        <v>51</v>
+      </c>
+      <c r="M139" t="s">
+        <v>52</v>
+      </c>
+      <c r="N139" t="s">
+        <v>53</v>
+      </c>
+      <c r="O139" t="s">
+        <v>54</v>
+      </c>
+      <c r="P139" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>72</v>
+      </c>
+      <c r="R139" t="s">
+        <v>52</v>
+      </c>
+      <c r="S139" t="s">
+        <v>73</v>
+      </c>
+      <c r="T139" t="s">
+        <v>90</v>
+      </c>
+      <c r="U139" t="s">
+        <v>682</v>
+      </c>
+      <c r="V139" t="s">
+        <v>92</v>
+      </c>
+      <c r="W139" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA139" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC139" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE139" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF139">
+        <v>1</v>
+      </c>
+      <c r="AG139" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH139" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI139" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ139">
+        <v>-940.49</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>-150.48</v>
+      </c>
+      <c r="AM139">
+        <v>0</v>
+      </c>
+      <c r="AN139">
+        <v>0</v>
+      </c>
+      <c r="AO139">
+        <v>0</v>
+      </c>
+      <c r="AP139">
+        <v>0</v>
+      </c>
+      <c r="AQ139">
+        <v>-1090.97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>9</v>
+      </c>
+      <c r="B140" t="s">
+        <v>43</v>
+      </c>
+      <c r="C140" t="s">
+        <v>683</v>
+      </c>
+      <c r="D140" t="s">
+        <v>611</v>
+      </c>
+      <c r="E140" t="s">
+        <v>196</v>
+      </c>
+      <c r="F140" t="s">
+        <v>46</v>
+      </c>
+      <c r="I140" t="s">
+        <v>87</v>
+      </c>
+      <c r="J140" t="s">
+        <v>684</v>
+      </c>
+      <c r="K140" t="s">
+        <v>685</v>
+      </c>
+      <c r="L140" t="s">
+        <v>51</v>
+      </c>
+      <c r="M140" t="s">
+        <v>52</v>
+      </c>
+      <c r="N140" t="s">
+        <v>53</v>
+      </c>
+      <c r="O140" t="s">
+        <v>54</v>
+      </c>
+      <c r="P140" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>72</v>
+      </c>
+      <c r="R140" t="s">
+        <v>52</v>
+      </c>
+      <c r="S140" t="s">
+        <v>73</v>
+      </c>
+      <c r="T140" t="s">
+        <v>90</v>
+      </c>
+      <c r="U140" t="s">
+        <v>686</v>
+      </c>
+      <c r="V140" t="s">
+        <v>92</v>
+      </c>
+      <c r="W140" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC140" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF140">
+        <v>1</v>
+      </c>
+      <c r="AG140" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH140" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI140" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ140">
+        <v>-470.25</v>
+      </c>
+      <c r="AK140">
+        <v>0</v>
+      </c>
+      <c r="AL140">
+        <v>-75.24</v>
+      </c>
+      <c r="AM140">
+        <v>0</v>
+      </c>
+      <c r="AN140">
+        <v>0</v>
+      </c>
+      <c r="AO140">
+        <v>0</v>
+      </c>
+      <c r="AP140">
+        <v>0</v>
+      </c>
+      <c r="AQ140">
+        <v>-545.49</v>
+      </c>
+    </row>
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>9</v>
+      </c>
+      <c r="B141" t="s">
+        <v>43</v>
+      </c>
+      <c r="C141" t="s">
+        <v>687</v>
+      </c>
+      <c r="D141" t="s">
+        <v>615</v>
+      </c>
+      <c r="E141" t="s">
+        <v>196</v>
+      </c>
+      <c r="F141" t="s">
+        <v>46</v>
+      </c>
+      <c r="I141" t="s">
+        <v>87</v>
+      </c>
+      <c r="J141" t="s">
+        <v>688</v>
+      </c>
+      <c r="K141" t="s">
+        <v>689</v>
+      </c>
+      <c r="L141" t="s">
+        <v>51</v>
+      </c>
+      <c r="M141" t="s">
+        <v>52</v>
+      </c>
+      <c r="N141" t="s">
+        <v>53</v>
+      </c>
+      <c r="O141" t="s">
+        <v>54</v>
+      </c>
+      <c r="P141" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>72</v>
+      </c>
+      <c r="R141" t="s">
+        <v>52</v>
+      </c>
+      <c r="S141" t="s">
+        <v>73</v>
+      </c>
+      <c r="T141" t="s">
+        <v>90</v>
+      </c>
+      <c r="U141" t="s">
+        <v>690</v>
+      </c>
+      <c r="V141" t="s">
+        <v>92</v>
+      </c>
+      <c r="W141" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA141" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE141" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF141">
+        <v>1</v>
+      </c>
+      <c r="AG141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH141" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI141" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ141">
+        <v>-3761.97</v>
+      </c>
+      <c r="AK141">
+        <v>0</v>
+      </c>
+      <c r="AL141">
+        <v>-601.92</v>
+      </c>
+      <c r="AM141">
+        <v>0</v>
+      </c>
+      <c r="AN141">
+        <v>0</v>
+      </c>
+      <c r="AO141">
+        <v>0</v>
+      </c>
+      <c r="AP141">
+        <v>0</v>
+      </c>
+      <c r="AQ141">
+        <v>-4363.89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>9</v>
+      </c>
+      <c r="B142" t="s">
+        <v>43</v>
+      </c>
+      <c r="C142" t="s">
+        <v>691</v>
+      </c>
+      <c r="D142" t="s">
+        <v>619</v>
+      </c>
+      <c r="E142" t="s">
+        <v>196</v>
+      </c>
+      <c r="F142" t="s">
+        <v>46</v>
+      </c>
+      <c r="I142" t="s">
+        <v>87</v>
+      </c>
+      <c r="J142" t="s">
+        <v>692</v>
+      </c>
+      <c r="K142" t="s">
+        <v>693</v>
+      </c>
+      <c r="L142" t="s">
+        <v>51</v>
+      </c>
+      <c r="M142" t="s">
+        <v>52</v>
+      </c>
+      <c r="N142" t="s">
+        <v>53</v>
+      </c>
+      <c r="O142" t="s">
+        <v>54</v>
+      </c>
+      <c r="P142" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>72</v>
+      </c>
+      <c r="R142" t="s">
+        <v>52</v>
+      </c>
+      <c r="S142" t="s">
+        <v>73</v>
+      </c>
+      <c r="T142" t="s">
+        <v>90</v>
+      </c>
+      <c r="U142" t="s">
+        <v>694</v>
+      </c>
+      <c r="V142" t="s">
+        <v>92</v>
+      </c>
+      <c r="W142" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA142" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC142" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE142" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF142">
+        <v>1</v>
+      </c>
+      <c r="AG142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH142" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI142" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ142">
+        <v>-94.05</v>
+      </c>
+      <c r="AK142">
+        <v>0</v>
+      </c>
+      <c r="AL142">
+        <v>-15.05</v>
+      </c>
+      <c r="AM142">
+        <v>0</v>
+      </c>
+      <c r="AN142">
+        <v>0</v>
+      </c>
+      <c r="AO142">
+        <v>0</v>
+      </c>
+      <c r="AP142">
+        <v>0</v>
+      </c>
+      <c r="AQ142">
+        <v>-109.1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>9</v>
+      </c>
+      <c r="B143" t="s">
+        <v>43</v>
+      </c>
+      <c r="C143" t="s">
+        <v>695</v>
+      </c>
+      <c r="D143" t="s">
+        <v>623</v>
+      </c>
+      <c r="E143" t="s">
+        <v>196</v>
+      </c>
+      <c r="F143" t="s">
+        <v>46</v>
+      </c>
+      <c r="I143" t="s">
+        <v>87</v>
+      </c>
+      <c r="J143" t="s">
+        <v>696</v>
+      </c>
+      <c r="K143" t="s">
+        <v>697</v>
+      </c>
+      <c r="L143" t="s">
+        <v>51</v>
+      </c>
+      <c r="M143" t="s">
+        <v>52</v>
+      </c>
+      <c r="N143" t="s">
+        <v>53</v>
+      </c>
+      <c r="O143" t="s">
+        <v>54</v>
+      </c>
+      <c r="P143" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>72</v>
+      </c>
+      <c r="R143" t="s">
+        <v>52</v>
+      </c>
+      <c r="S143" t="s">
+        <v>73</v>
+      </c>
+      <c r="T143" t="s">
+        <v>90</v>
+      </c>
+      <c r="U143" t="s">
+        <v>698</v>
+      </c>
+      <c r="V143" t="s">
+        <v>92</v>
+      </c>
+      <c r="W143" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA143" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC143" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE143" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF143">
+        <v>1</v>
+      </c>
+      <c r="AG143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH143" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI143" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ143">
+        <v>-282.15</v>
+      </c>
+      <c r="AK143">
+        <v>0</v>
+      </c>
+      <c r="AL143">
+        <v>-45.14</v>
+      </c>
+      <c r="AM143">
+        <v>0</v>
+      </c>
+      <c r="AN143">
+        <v>0</v>
+      </c>
+      <c r="AO143">
+        <v>0</v>
+      </c>
+      <c r="AP143">
+        <v>0</v>
+      </c>
+      <c r="AQ143">
+        <v>-327.29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>9</v>
+      </c>
+      <c r="B144" t="s">
+        <v>43</v>
+      </c>
+      <c r="C144" t="s">
+        <v>699</v>
+      </c>
+      <c r="D144" t="s">
+        <v>627</v>
+      </c>
+      <c r="E144" t="s">
+        <v>196</v>
+      </c>
+      <c r="F144" t="s">
+        <v>46</v>
+      </c>
+      <c r="I144" t="s">
+        <v>87</v>
+      </c>
+      <c r="J144" t="s">
+        <v>700</v>
+      </c>
+      <c r="K144" t="s">
+        <v>701</v>
+      </c>
+      <c r="L144" t="s">
+        <v>51</v>
+      </c>
+      <c r="M144" t="s">
+        <v>52</v>
+      </c>
+      <c r="N144" t="s">
+        <v>53</v>
+      </c>
+      <c r="O144" t="s">
+        <v>54</v>
+      </c>
+      <c r="P144" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>72</v>
+      </c>
+      <c r="R144" t="s">
+        <v>52</v>
+      </c>
+      <c r="S144" t="s">
+        <v>73</v>
+      </c>
+      <c r="T144" t="s">
+        <v>90</v>
+      </c>
+      <c r="U144" t="s">
+        <v>702</v>
+      </c>
+      <c r="V144" t="s">
+        <v>92</v>
+      </c>
+      <c r="W144" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA144" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC144" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE144" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF144">
+        <v>1</v>
+      </c>
+      <c r="AG144" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH144" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI144" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ144">
+        <v>-940.49</v>
+      </c>
+      <c r="AK144">
+        <v>0</v>
+      </c>
+      <c r="AL144">
+        <v>-150.48</v>
+      </c>
+      <c r="AM144">
+        <v>0</v>
+      </c>
+      <c r="AN144">
+        <v>0</v>
+      </c>
+      <c r="AO144">
+        <v>0</v>
+      </c>
+      <c r="AP144">
+        <v>0</v>
+      </c>
+      <c r="AQ144">
+        <v>-1090.97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>9</v>
+      </c>
+      <c r="B145" t="s">
+        <v>43</v>
+      </c>
+      <c r="C145" t="s">
+        <v>703</v>
+      </c>
+      <c r="D145" t="s">
+        <v>631</v>
+      </c>
+      <c r="E145" t="s">
+        <v>196</v>
+      </c>
+      <c r="F145" t="s">
+        <v>46</v>
+      </c>
+      <c r="I145" t="s">
+        <v>87</v>
+      </c>
+      <c r="J145" t="s">
+        <v>704</v>
+      </c>
+      <c r="K145" t="s">
+        <v>705</v>
+      </c>
+      <c r="L145" t="s">
+        <v>51</v>
+      </c>
+      <c r="M145" t="s">
+        <v>52</v>
+      </c>
+      <c r="N145" t="s">
+        <v>53</v>
+      </c>
+      <c r="O145" t="s">
+        <v>54</v>
+      </c>
+      <c r="P145" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>72</v>
+      </c>
+      <c r="R145" t="s">
+        <v>52</v>
+      </c>
+      <c r="S145" t="s">
+        <v>73</v>
+      </c>
+      <c r="T145" t="s">
+        <v>90</v>
+      </c>
+      <c r="U145" t="s">
+        <v>706</v>
+      </c>
+      <c r="V145" t="s">
+        <v>92</v>
+      </c>
+      <c r="W145" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA145" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC145" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE145" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF145">
+        <v>1</v>
+      </c>
+      <c r="AG145" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH145" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI145" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ145">
+        <v>-940.49</v>
+      </c>
+      <c r="AK145">
+        <v>0</v>
+      </c>
+      <c r="AL145">
+        <v>-150.48</v>
+      </c>
+      <c r="AM145">
+        <v>0</v>
+      </c>
+      <c r="AN145">
+        <v>0</v>
+      </c>
+      <c r="AO145">
+        <v>0</v>
+      </c>
+      <c r="AP145">
+        <v>0</v>
+      </c>
+      <c r="AQ145">
+        <v>-1090.97</v>
+      </c>
+    </row>
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>9</v>
+      </c>
+      <c r="B146" t="s">
+        <v>43</v>
+      </c>
+      <c r="C146" t="s">
+        <v>707</v>
+      </c>
+      <c r="D146" t="s">
+        <v>635</v>
+      </c>
+      <c r="E146" t="s">
+        <v>196</v>
+      </c>
+      <c r="F146" t="s">
+        <v>46</v>
+      </c>
+      <c r="I146" t="s">
+        <v>87</v>
+      </c>
+      <c r="J146" t="s">
+        <v>708</v>
+      </c>
+      <c r="K146" t="s">
+        <v>709</v>
+      </c>
+      <c r="L146" t="s">
+        <v>51</v>
+      </c>
+      <c r="M146" t="s">
+        <v>52</v>
+      </c>
+      <c r="N146" t="s">
+        <v>53</v>
+      </c>
+      <c r="O146" t="s">
+        <v>54</v>
+      </c>
+      <c r="P146" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>72</v>
+      </c>
+      <c r="R146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S146" t="s">
+        <v>73</v>
+      </c>
+      <c r="T146" t="s">
+        <v>90</v>
+      </c>
+      <c r="U146" t="s">
+        <v>710</v>
+      </c>
+      <c r="V146" t="s">
+        <v>92</v>
+      </c>
+      <c r="W146" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA146" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC146" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE146" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF146">
+        <v>1</v>
+      </c>
+      <c r="AG146" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH146" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI146" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ146">
+        <v>-1128.59</v>
+      </c>
+      <c r="AK146">
+        <v>0</v>
+      </c>
+      <c r="AL146">
+        <v>-180.57</v>
+      </c>
+      <c r="AM146">
+        <v>0</v>
+      </c>
+      <c r="AN146">
+        <v>0</v>
+      </c>
+      <c r="AO146">
+        <v>0</v>
+      </c>
+      <c r="AP146">
+        <v>0</v>
+      </c>
+      <c r="AQ146">
+        <v>-1309.16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>9</v>
+      </c>
+      <c r="B147" t="s">
+        <v>43</v>
+      </c>
+      <c r="C147" t="s">
+        <v>711</v>
+      </c>
+      <c r="D147" t="s">
+        <v>639</v>
+      </c>
+      <c r="E147" t="s">
+        <v>196</v>
+      </c>
+      <c r="F147" t="s">
+        <v>46</v>
+      </c>
+      <c r="I147" t="s">
+        <v>87</v>
+      </c>
+      <c r="J147" t="s">
+        <v>712</v>
+      </c>
+      <c r="K147" t="s">
+        <v>713</v>
+      </c>
+      <c r="L147" t="s">
+        <v>51</v>
+      </c>
+      <c r="M147" t="s">
+        <v>52</v>
+      </c>
+      <c r="N147" t="s">
+        <v>53</v>
+      </c>
+      <c r="O147" t="s">
+        <v>54</v>
+      </c>
+      <c r="P147" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>72</v>
+      </c>
+      <c r="R147" t="s">
+        <v>52</v>
+      </c>
+      <c r="S147" t="s">
+        <v>73</v>
+      </c>
+      <c r="T147" t="s">
+        <v>90</v>
+      </c>
+      <c r="U147" t="s">
+        <v>714</v>
+      </c>
+      <c r="V147" t="s">
+        <v>92</v>
+      </c>
+      <c r="W147" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA147" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE147" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF147">
+        <v>1</v>
+      </c>
+      <c r="AG147" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH147" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI147" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ147">
+        <v>-1410.74</v>
+      </c>
+      <c r="AK147">
+        <v>0</v>
+      </c>
+      <c r="AL147">
+        <v>-225.72</v>
+      </c>
+      <c r="AM147">
+        <v>0</v>
+      </c>
+      <c r="AN147">
+        <v>0</v>
+      </c>
+      <c r="AO147">
+        <v>0</v>
+      </c>
+      <c r="AP147">
+        <v>0</v>
+      </c>
+      <c r="AQ147">
+        <v>-1636.46</v>
+      </c>
+    </row>
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>9</v>
+      </c>
+      <c r="B148" t="s">
+        <v>43</v>
+      </c>
+      <c r="C148" t="s">
+        <v>715</v>
+      </c>
+      <c r="D148" t="s">
+        <v>643</v>
+      </c>
+      <c r="E148" t="s">
+        <v>196</v>
+      </c>
+      <c r="F148" t="s">
+        <v>46</v>
+      </c>
+      <c r="I148" t="s">
+        <v>87</v>
+      </c>
+      <c r="J148" t="s">
+        <v>716</v>
+      </c>
+      <c r="K148" t="s">
+        <v>717</v>
+      </c>
+      <c r="L148" t="s">
+        <v>51</v>
+      </c>
+      <c r="M148" t="s">
+        <v>52</v>
+      </c>
+      <c r="N148" t="s">
+        <v>53</v>
+      </c>
+      <c r="O148" t="s">
+        <v>54</v>
+      </c>
+      <c r="P148" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>72</v>
+      </c>
+      <c r="R148" t="s">
+        <v>52</v>
+      </c>
+      <c r="S148" t="s">
+        <v>73</v>
+      </c>
+      <c r="T148" t="s">
+        <v>90</v>
+      </c>
+      <c r="U148" t="s">
+        <v>718</v>
+      </c>
+      <c r="V148" t="s">
+        <v>92</v>
+      </c>
+      <c r="W148" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA148" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC148" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE148" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF148">
+        <v>1</v>
+      </c>
+      <c r="AG148" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH148" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI148" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ148">
+        <v>-564.3</v>
+      </c>
+      <c r="AK148">
+        <v>0</v>
+      </c>
+      <c r="AL148">
+        <v>-90.29</v>
+      </c>
+      <c r="AM148">
+        <v>0</v>
+      </c>
+      <c r="AN148">
+        <v>0</v>
+      </c>
+      <c r="AO148">
+        <v>0</v>
+      </c>
+      <c r="AP148">
+        <v>0</v>
+      </c>
+      <c r="AQ148">
+        <v>-654.59</v>
+      </c>
+    </row>
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>9</v>
+      </c>
+      <c r="B149" t="s">
+        <v>43</v>
+      </c>
+      <c r="C149" t="s">
+        <v>719</v>
+      </c>
+      <c r="D149" t="s">
+        <v>45</v>
+      </c>
+      <c r="F149" t="s">
+        <v>46</v>
+      </c>
+      <c r="H149" t="s">
+        <v>720</v>
+      </c>
+      <c r="I149" t="s">
+        <v>48</v>
+      </c>
+      <c r="J149" t="s">
+        <v>721</v>
+      </c>
+      <c r="K149" t="s">
+        <v>722</v>
+      </c>
+      <c r="L149" t="s">
+        <v>51</v>
+      </c>
+      <c r="M149" t="s">
+        <v>52</v>
+      </c>
+      <c r="N149" t="s">
+        <v>53</v>
+      </c>
+      <c r="O149" t="s">
+        <v>54</v>
+      </c>
+      <c r="P149" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>572</v>
+      </c>
+      <c r="R149" t="s">
+        <v>573</v>
+      </c>
+      <c r="S149" t="s">
+        <v>574</v>
+      </c>
+      <c r="T149" t="s">
+        <v>575</v>
+      </c>
+      <c r="U149" t="s">
+        <v>723</v>
+      </c>
+      <c r="V149" t="s">
+        <v>60</v>
+      </c>
+      <c r="W149" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA149" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC149" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE149" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF149">
+        <v>1</v>
+      </c>
+      <c r="AG149" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH149" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI149" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ149">
+        <v>453996.27</v>
+      </c>
+      <c r="AK149">
+        <v>0</v>
+      </c>
+      <c r="AL149">
+        <v>72639.4</v>
+      </c>
+      <c r="AM149">
+        <v>0</v>
+      </c>
+      <c r="AN149">
+        <v>0</v>
+      </c>
+      <c r="AO149">
+        <v>0</v>
+      </c>
+      <c r="AP149">
+        <v>3207.12</v>
+      </c>
+      <c r="AQ149">
+        <v>523428.55</v>
+      </c>
+    </row>
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>9</v>
+      </c>
+      <c r="B150" t="s">
+        <v>43</v>
+      </c>
+      <c r="C150" t="s">
+        <v>724</v>
+      </c>
+      <c r="D150" t="s">
+        <v>45</v>
+      </c>
+      <c r="F150" t="s">
+        <v>46</v>
+      </c>
+      <c r="H150" t="s">
+        <v>725</v>
+      </c>
+      <c r="I150" t="s">
+        <v>48</v>
+      </c>
+      <c r="J150" t="s">
+        <v>726</v>
+      </c>
+      <c r="K150" t="s">
+        <v>727</v>
+      </c>
+      <c r="L150" t="s">
+        <v>51</v>
+      </c>
+      <c r="M150" t="s">
+        <v>52</v>
+      </c>
+      <c r="N150" t="s">
+        <v>53</v>
+      </c>
+      <c r="O150" t="s">
+        <v>54</v>
+      </c>
+      <c r="P150" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>56</v>
+      </c>
+      <c r="R150" t="s">
+        <v>52</v>
+      </c>
+      <c r="S150" t="s">
+        <v>57</v>
+      </c>
+      <c r="T150" t="s">
+        <v>193</v>
+      </c>
+      <c r="U150" t="s">
+        <v>728</v>
+      </c>
+      <c r="V150" t="s">
+        <v>60</v>
+      </c>
+      <c r="W150" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA150" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC150" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE150" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF150">
+        <v>1</v>
+      </c>
+      <c r="AG150" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH150" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI150" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ150">
+        <v>754963.5</v>
+      </c>
+      <c r="AK150">
+        <v>0</v>
+      </c>
+      <c r="AL150">
+        <v>120794.16</v>
+      </c>
+      <c r="AM150">
+        <v>0</v>
+      </c>
+      <c r="AN150">
+        <v>0</v>
+      </c>
+      <c r="AO150">
+        <v>0</v>
+      </c>
+      <c r="AP150">
+        <v>0</v>
+      </c>
+      <c r="AQ150">
+        <v>875757.66</v>
+      </c>
+    </row>
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>9</v>
+      </c>
+      <c r="B151" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" t="s">
+        <v>729</v>
+      </c>
+      <c r="D151" t="s">
+        <v>719</v>
+      </c>
+      <c r="E151" t="s">
+        <v>730</v>
+      </c>
+      <c r="F151" t="s">
+        <v>46</v>
+      </c>
+      <c r="H151" t="s">
+        <v>731</v>
+      </c>
+      <c r="I151" t="s">
+        <v>48</v>
+      </c>
+      <c r="J151" t="s">
+        <v>732</v>
+      </c>
+      <c r="K151" t="s">
+        <v>733</v>
+      </c>
+      <c r="L151" t="s">
+        <v>51</v>
+      </c>
+      <c r="M151" t="s">
+        <v>52</v>
+      </c>
+      <c r="N151" t="s">
+        <v>53</v>
+      </c>
+      <c r="O151" t="s">
+        <v>54</v>
+      </c>
+      <c r="P151" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>572</v>
+      </c>
+      <c r="R151" t="s">
+        <v>573</v>
+      </c>
+      <c r="S151" t="s">
+        <v>574</v>
+      </c>
+      <c r="T151" t="s">
+        <v>575</v>
+      </c>
+      <c r="U151" t="s">
+        <v>734</v>
+      </c>
+      <c r="V151" t="s">
+        <v>60</v>
+      </c>
+      <c r="W151" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>735</v>
+      </c>
+      <c r="AA151" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB151" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC151" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD151" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE151" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF151">
+        <v>1</v>
+      </c>
+      <c r="AG151" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH151" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI151" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ151">
+        <v>454001.35</v>
+      </c>
+      <c r="AK151">
+        <v>0</v>
+      </c>
+      <c r="AL151">
+        <v>72640.22</v>
+      </c>
+      <c r="AM151">
+        <v>0</v>
+      </c>
+      <c r="AN151">
+        <v>0</v>
+      </c>
+      <c r="AO151">
+        <v>0</v>
+      </c>
+      <c r="AP151">
+        <v>3207.12</v>
+      </c>
+      <c r="AQ151">
+        <v>523434.45</v>
+      </c>
+    </row>
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
+        <v>43</v>
+      </c>
+      <c r="C152" t="s">
+        <v>736</v>
+      </c>
+      <c r="D152" t="s">
+        <v>45</v>
+      </c>
+      <c r="F152" t="s">
+        <v>46</v>
+      </c>
+      <c r="H152" t="s">
+        <v>737</v>
+      </c>
+      <c r="I152" t="s">
+        <v>48</v>
+      </c>
+      <c r="J152" t="s">
+        <v>738</v>
+      </c>
+      <c r="K152" t="s">
+        <v>739</v>
+      </c>
+      <c r="L152" t="s">
+        <v>51</v>
+      </c>
+      <c r="M152" t="s">
+        <v>52</v>
+      </c>
+      <c r="N152" t="s">
+        <v>53</v>
+      </c>
+      <c r="O152" t="s">
+        <v>54</v>
+      </c>
+      <c r="P152" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>572</v>
+      </c>
+      <c r="R152" t="s">
+        <v>573</v>
+      </c>
+      <c r="S152" t="s">
+        <v>574</v>
+      </c>
+      <c r="T152" t="s">
+        <v>575</v>
+      </c>
+      <c r="U152" t="s">
+        <v>734</v>
+      </c>
+      <c r="V152" t="s">
+        <v>60</v>
+      </c>
+      <c r="W152" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>740</v>
+      </c>
+      <c r="AA152" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB152" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC152" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD152" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE152" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF152">
+        <v>1</v>
+      </c>
+      <c r="AG152" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH152" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI152" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ152">
+        <v>454001.35</v>
+      </c>
+      <c r="AK152">
+        <v>0</v>
+      </c>
+      <c r="AL152">
+        <v>72640.22</v>
+      </c>
+      <c r="AM152">
+        <v>0</v>
+      </c>
+      <c r="AN152">
+        <v>0</v>
+      </c>
+      <c r="AO152">
+        <v>0</v>
+      </c>
+      <c r="AP152">
+        <v>3207.15</v>
+      </c>
+      <c r="AQ152">
+        <v>523434.42</v>
+      </c>
+    </row>
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>9</v>
+      </c>
+      <c r="B153" t="s">
+        <v>43</v>
+      </c>
+      <c r="C153" t="s">
+        <v>741</v>
+      </c>
+      <c r="D153" t="s">
+        <v>719</v>
+      </c>
+      <c r="E153" t="s">
+        <v>730</v>
+      </c>
+      <c r="F153" t="s">
+        <v>46</v>
+      </c>
+      <c r="H153" t="s">
+        <v>742</v>
+      </c>
+      <c r="I153" t="s">
+        <v>48</v>
+      </c>
+      <c r="J153" t="s">
+        <v>743</v>
+      </c>
+      <c r="K153" t="s">
+        <v>744</v>
+      </c>
+      <c r="L153" t="s">
+        <v>51</v>
+      </c>
+      <c r="M153" t="s">
+        <v>52</v>
+      </c>
+      <c r="N153" t="s">
+        <v>53</v>
+      </c>
+      <c r="O153" t="s">
+        <v>54</v>
+      </c>
+      <c r="P153" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>572</v>
+      </c>
+      <c r="R153" t="s">
+        <v>573</v>
+      </c>
+      <c r="S153" t="s">
+        <v>574</v>
+      </c>
+      <c r="T153" t="s">
+        <v>575</v>
+      </c>
+      <c r="U153" t="s">
+        <v>734</v>
+      </c>
+      <c r="V153" t="s">
+        <v>60</v>
+      </c>
+      <c r="W153" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>745</v>
+      </c>
+      <c r="AA153" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB153" t="s">
+        <v>746</v>
+      </c>
+      <c r="AC153" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE153" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF153">
+        <v>1</v>
+      </c>
+      <c r="AG153" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH153" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI153" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ153">
+        <v>454001.35</v>
+      </c>
+      <c r="AK153">
+        <v>0</v>
+      </c>
+      <c r="AL153">
+        <v>72640.22</v>
+      </c>
+      <c r="AM153">
+        <v>0</v>
+      </c>
+      <c r="AN153">
+        <v>0</v>
+      </c>
+      <c r="AO153">
+        <v>0</v>
+      </c>
+      <c r="AP153">
+        <v>3207.15</v>
+      </c>
+      <c r="AQ153">
+        <v>523434.42</v>
+      </c>
+    </row>
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
+        <v>43</v>
+      </c>
+      <c r="C154" t="s">
+        <v>747</v>
+      </c>
+      <c r="D154" t="s">
+        <v>719</v>
+      </c>
+      <c r="E154" t="s">
+        <v>730</v>
+      </c>
+      <c r="F154" t="s">
+        <v>46</v>
+      </c>
+      <c r="H154" t="s">
+        <v>748</v>
+      </c>
+      <c r="I154" t="s">
+        <v>48</v>
+      </c>
+      <c r="J154" t="s">
+        <v>749</v>
+      </c>
+      <c r="K154" t="s">
+        <v>750</v>
+      </c>
+      <c r="L154" t="s">
+        <v>51</v>
+      </c>
+      <c r="M154" t="s">
+        <v>52</v>
+      </c>
+      <c r="N154" t="s">
+        <v>53</v>
+      </c>
+      <c r="O154" t="s">
+        <v>54</v>
+      </c>
+      <c r="P154" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>572</v>
+      </c>
+      <c r="R154" t="s">
+        <v>573</v>
+      </c>
+      <c r="S154" t="s">
+        <v>574</v>
+      </c>
+      <c r="T154" t="s">
+        <v>575</v>
+      </c>
+      <c r="U154" t="s">
+        <v>751</v>
+      </c>
+      <c r="V154" t="s">
+        <v>60</v>
+      </c>
+      <c r="W154" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA154" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC154" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE154" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF154">
+        <v>1</v>
+      </c>
+      <c r="AG154" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH154" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI154" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ154">
+        <v>454001.35</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>72640.22</v>
+      </c>
+      <c r="AM154">
+        <v>0</v>
+      </c>
+      <c r="AN154">
+        <v>0</v>
+      </c>
+      <c r="AO154">
+        <v>0</v>
+      </c>
+      <c r="AP154">
+        <v>3207.15</v>
+      </c>
+      <c r="AQ154">
+        <v>523434.42</v>
+      </c>
+    </row>
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>10</v>
+      </c>
+      <c r="B155" t="s">
+        <v>43</v>
+      </c>
+      <c r="C155" t="s">
+        <v>752</v>
+      </c>
+      <c r="D155" t="s">
+        <v>45</v>
+      </c>
+      <c r="F155" t="s">
+        <v>46</v>
+      </c>
+      <c r="H155" t="s">
+        <v>753</v>
+      </c>
+      <c r="I155" t="s">
+        <v>48</v>
+      </c>
+      <c r="J155" t="s">
+        <v>754</v>
+      </c>
+      <c r="K155" t="s">
+        <v>755</v>
+      </c>
+      <c r="L155" t="s">
+        <v>51</v>
+      </c>
+      <c r="M155" t="s">
+        <v>52</v>
+      </c>
+      <c r="N155" t="s">
+        <v>53</v>
+      </c>
+      <c r="O155" t="s">
+        <v>54</v>
+      </c>
+      <c r="P155" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>572</v>
+      </c>
+      <c r="R155" t="s">
+        <v>573</v>
+      </c>
+      <c r="S155" t="s">
+        <v>574</v>
+      </c>
+      <c r="T155" t="s">
+        <v>575</v>
+      </c>
+      <c r="U155" t="s">
+        <v>756</v>
+      </c>
+      <c r="V155" t="s">
+        <v>60</v>
+      </c>
+      <c r="W155" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>757</v>
+      </c>
+      <c r="AA155" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB155" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC155" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD155" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE155" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF155">
+        <v>1</v>
+      </c>
+      <c r="AG155" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH155" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI155" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ155">
+        <v>7998036.27</v>
+      </c>
+      <c r="AK155">
+        <v>0</v>
+      </c>
+      <c r="AL155">
+        <v>1279685.8</v>
+      </c>
+      <c r="AM155">
+        <v>0</v>
+      </c>
+      <c r="AN155">
+        <v>0</v>
+      </c>
+      <c r="AO155">
+        <v>0</v>
+      </c>
+      <c r="AP155">
+        <v>39844.35</v>
+      </c>
+      <c r="AQ155">
+        <v>9237877.72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>10</v>
+      </c>
+      <c r="B156" t="s">
+        <v>43</v>
+      </c>
+      <c r="C156" t="s">
+        <v>758</v>
+      </c>
+      <c r="D156" t="s">
+        <v>45</v>
+      </c>
+      <c r="F156" t="s">
+        <v>46</v>
+      </c>
+      <c r="H156" t="s">
+        <v>759</v>
+      </c>
+      <c r="I156" t="s">
+        <v>48</v>
+      </c>
+      <c r="J156" t="s">
+        <v>760</v>
+      </c>
+      <c r="K156" t="s">
+        <v>761</v>
+      </c>
+      <c r="L156" t="s">
+        <v>51</v>
+      </c>
+      <c r="M156" t="s">
+        <v>52</v>
+      </c>
+      <c r="N156" t="s">
+        <v>53</v>
+      </c>
+      <c r="O156" t="s">
+        <v>54</v>
+      </c>
+      <c r="P156" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>572</v>
+      </c>
+      <c r="R156" t="s">
+        <v>573</v>
+      </c>
+      <c r="S156" t="s">
+        <v>574</v>
+      </c>
+      <c r="T156" t="s">
+        <v>575</v>
+      </c>
+      <c r="U156" t="s">
+        <v>762</v>
+      </c>
+      <c r="V156" t="s">
+        <v>60</v>
+      </c>
+      <c r="W156" t="s">
+        <v>577</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA156" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC156" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE156" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF156">
+        <v>1</v>
+      </c>
+      <c r="AG156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH156" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI156" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ156">
+        <v>7998036.27</v>
+      </c>
+      <c r="AK156">
+        <v>0</v>
+      </c>
+      <c r="AL156">
+        <v>1279685.8</v>
+      </c>
+      <c r="AM156">
+        <v>0</v>
+      </c>
+      <c r="AN156">
+        <v>0</v>
+      </c>
+      <c r="AO156">
+        <v>0</v>
+      </c>
+      <c r="AP156">
+        <v>39844.35</v>
+      </c>
+      <c r="AQ156">
+        <v>9237877.72</v>
       </c>
     </row>
   </sheetData>
